--- a/daily_matches/job_matches_2026-06-17.xlsx
+++ b/daily_matches/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ruby on Rails Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Program Management Solutions</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
+          <t>https://www.indeed.com/viewjob?jk=a78e7dca5038b723</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Risk Data Scientist</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Snowflake, PySpark, Kafka</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Data Lake, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1077cf7a91ad9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer Sr. (mid-career)</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e592e82101f13d55</t>
+          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Full Stack Customer Data Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift</t>
+          <t>RAG, Copilot, Dataflow, Docker, Kubernetes, Git, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9829caa42dfe5189</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Software Engineer - Chicago, IL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, CI/CD, Snowflake, Hadoop, Tableau, Power BI, Python, SQL</t>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2f0e62d788eb2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist 1</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Python</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba96d483cabc875</t>
+          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>LLM-Based Knowledge Extraction and Failure Analysis Internship</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Azure ML, EC2, Docker, Git, Snowflake, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Apache Airflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d579dc4d6d711bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7831c8cf1b9fbf3c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BlueSight</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Azure ML, EC2, Docker, Git, Snowflake, Python, SQL</t>
+          <t>Data Scientist, RAG, Glue, Athena, MLflow, FastAPI, Docker, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7660c2fee91a1dd</t>
+          <t>https://www.indeed.com/viewjob?jk=81c05c2dd42c01db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI-First- Software Engineer</t>
+          <t>Machine Learning Engineer (Agent &amp; Inference) - (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConsumerAffairs</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd5da8c39d0e233</t>
+          <t>https://www.indeed.com/viewjob?jk=593002a905391e36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Agentic AI, LLM Evaluation, and Trustworthy Systems Research Internship</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c360c32a7100140</t>
+          <t>https://www.indeed.com/viewjob?jk=0bad8b86323f2c00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Full Stack SDE - SMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d39256eef4e93</t>
+          <t>https://www.indeed.com/viewjob?jk=cf424902c6cd5d2b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior SDET II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23f48667102b94a</t>
+          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Google Cloud AI Solutions Architect, Gemini Enterprise</t>
+          <t>Senior Software Engineer, Backend/Infra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Gemini, Prompt Engineering, BigQuery, CI/CD, BigQuery, Python, R, Java</t>
+          <t>Generative AI, LangChain, Gemini, Prompt Engineering, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b24c41a24e1339</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb9d9b1e56e523d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961d00a83fa0b14f</t>
+          <t>https://www.indeed.com/viewjob?jk=974c2829b0ad8261</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rapid Eagle Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Redshift, Synapse, CI/CD, Terraform, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d3856211d8928</t>
+          <t>https://www.indeed.com/viewjob?jk=d405b0cfa63ccb4d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Agentic Developer</t>
+          <t>AI Engineers</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>Accellor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ddeed7e6349d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb7184c42c292bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Agentic Developer</t>
+          <t>AI Engineers</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>Accellor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1df3075064d0f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1207c7b863e43e8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Agentic Developer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f407931e54b160bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Agentic Developer</t>
+          <t>Sr. DevOps Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f0dcc39d7ecafb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b6b4527d661c599</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a2dea654b3367d</t>
+          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Marketing &amp; Consumer Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Optimization</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7055e58cc531eb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1cfede546d24f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Computer Scientist / Software Developer</t>
+          <t>Senior Associate, Data Scientist - People Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Integrated Solutions for Systems</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9811a936f375760e</t>
+          <t>https://www.indeed.com/viewjob?jk=9045df2a6f462ae3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Computer Scientist / Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Integrated Solutions for Systems</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e542e23dd14c34ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>System and Software Optimization Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e817c9a33f8b8c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Algorithm Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>SymphonyAI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Prompt Engineering, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa354644f4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=754f36beabf7c335</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applied Artificial Intelligence (AI) Engineer</t>
+          <t>Senior Security Engineer - Data Security</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sensata Technologies, Inc.</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Home, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FastAPI, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae24cbf321cecafe</t>
+          <t>https://www.indeed.com/viewjob?jk=1f9cd016b153874c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Junior Full Stack Data Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mojo Family of Brands</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, Glue, Docker, Terraform, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
+          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Architect -Professional services(USA remote based)</t>
+          <t>Marketing Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Gabb Wireless</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ea40d323d76dcb</t>
+          <t>https://www.indeed.com/viewjob?jk=6813dcc9401d22dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Orchestration &amp; Job Execution</t>
+          <t>(Remote) Senior Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ad87124291af72</t>
+          <t>https://www.indeed.com/viewjob?jk=6040e41e217186c1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer III, Popeyes</t>
+          <t>Senior Plasma Control Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Thea Energy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kearny, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, AKS, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cd8c2c2c1296a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ca172443d2abb72</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bitus Labs LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, MongoDB, Python, SQL, R, Scala, Optimization</t>
+          <t>Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab4c08e624f526e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Digital Assets Engineer</t>
+          <t>Enterprise Solutions Architect, Engineering Platform Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Jenkins, Git, SQL, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6283c363950ab587</t>
+          <t>https://www.indeed.com/viewjob?jk=f4305f88ccda4c4f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0e90df4c8ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=58b0461d8675cd72</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Litehouse Foods, Inc.</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sandpoint, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,42 +1651,357 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab38423aad8ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=95b8a3a56374989a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Generative AI developer</t>
+          <t>Program Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>Amerit Fleet Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Tableau, Power BI, Quicksight, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd7811a03bc60fca</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mid-level Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Teknoluxion</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, AWS SageMaker, S3, Glue, Kafka, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dc74ac325008850</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Medallia Strategy Analytics, Analyst</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medallia</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=279ab2d1e0ede600</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer, StorageGRID</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9a6259b3296d73</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, CI/CD, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b9a7cc93e281359</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Information Security Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PROBABLYMONSTERS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a31a6affadc5dff7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer Co-Op</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaf5705f20c99989</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer Co-Op</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24b448b6b31cd3a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior AI Scientist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c5ef7572f1319eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior AI Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ddbda58dfd9e21a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-17.xlsx
+++ b/daily_matches/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Sr. Engineer, Data - Archimedes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78e7dca5038b723</t>
+          <t>https://www.indeed.com/viewjob?jk=42d62482ae7cddd2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Data Lake, Git, BigQuery</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3749a31d1864c73</t>
+          <t>https://www.indeed.com/viewjob?jk=dbffc0979d491df9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03af74475287b0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=863d1330bc4e06b9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Full Stack Customer Data Developer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Dataflow, Docker, Kubernetes, Git, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc517f42c43516c</t>
+          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Chicago, IL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1773eff14944c55</t>
+          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Generative AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, Docker, Kubernetes, Apache Airflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351fc9ced107d0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LLM-Based Knowledge Extraction and Failure Analysis Internship</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Apache Airflow</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7831c8cf1b9fbf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BlueSight</t>
+          <t>Menlo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Athena, MLflow, FastAPI, Docker, CI/CD, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c05c2dd42c01db</t>
+          <t>https://www.indeed.com/viewjob?jk=25dea91fa4f468b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent &amp; Inference) - (Chinese Mandarin Speaker)</t>
+          <t>Cloud Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bitus Labs LLC</t>
+          <t>Cloudforce</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>National Harbor, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, LLaMA, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Hadoop, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593002a905391e36</t>
+          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agentic AI, LLM Evaluation, and Trustworthy Systems Research Internship</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Generative AI, RAG, Copilot, Data Lake, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bad8b86323f2c00</t>
+          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Full Stack SDE - SMA</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>The Linux Foundation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf424902c6cd5d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior SDET II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL</t>
+          <t>S3, Athena, Redshift, CI/CD, Terraform, Git, Redshift, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805612b772f38e45</t>
+          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Infra</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Gemini, Prompt Engineering, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, AKS, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb9d9b1e56e523d</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>AI Developer, SA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Snowflake, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Snowflake, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=974c2829b0ad8261</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3bc996c009755</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Development Engineer in Test, ML/AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rapid Eagle Inc</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Redshift, Synapse, CI/CD, Terraform, Git, Snowflake, Redshift</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d405b0cfa63ccb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineers</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Accellor</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Power BI, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb7184c42c292bd</t>
+          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineers</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accellor</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, Python</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1207c7b863e43e8</t>
+          <t>https://www.indeed.com/viewjob?jk=44241dafdd1e9110</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R</t>
+          <t>Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, NLTK, CI/CD, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa38d65a2e3ff72</t>
+          <t>https://www.indeed.com/viewjob?jk=b112a1e1ee57ad24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Platform</t>
+          <t>Software Engineer (Quality Assurance/SDET Focus)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Kafka, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b6b4527d661c599</t>
+          <t>https://www.indeed.com/viewjob?jk=957fb31284f4375c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0092170302c322f0</t>
+          <t>https://www.indeed.com/viewjob?jk=37dc06c5e4d512c4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate, Data Scientist - People Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1cfede546d24f4</t>
+          <t>https://www.indeed.com/viewjob?jk=be0efa2f7bb9ed87</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - People Strategy &amp; Analytics</t>
+          <t>Data Scientist / Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, MLflow, CI/CD, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9045df2a6f462ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/ML Engineer/ AI Ops Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4983335721888ff</t>
+          <t>https://www.indeed.com/viewjob?jk=854a4d3726897368</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Scientist II, Data Science – Behavioral Marketing Analytics &amp; Customer Insights</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb61f925af04493f</t>
+          <t>https://www.indeed.com/viewjob?jk=3da4d55e5bd9e628</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Scientist II, Data Science – Behavioral Marketing Analytics &amp; Customer Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SymphonyAI</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f36beabf7c335</t>
+          <t>https://www.indeed.com/viewjob?jk=98562f66128c6f6d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Data Security</t>
+          <t>Commercial Solution Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,651 +1357,56 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9cd016b153874c</t>
+          <t>https://www.indeed.com/viewjob?jk=a50d2aae1ab24a68</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c1ddb2ef420b3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Marketing Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Gabb Wireless</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6813dcc9401d22dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>(Remote) Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Harris Computer</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6040e41e217186c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Plasma Control Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Thea Energy</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Kearny, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, AKS, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ca172443d2abb72</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Analyst — Game Analytics (Chinese Mandarin Speaker)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Bitus Labs LLC</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6505d408020fe2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Enterprise Solutions Architect, Engineering Platform Services</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4305f88ccda4c4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>DocuSign</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b0461d8675cd72</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Assurant</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95b8a3a56374989a</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Program Analyst</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Amerit Fleet Solutions</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Tableau, Power BI, Quicksight, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7811a03bc60fca</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Mid-level Data Scientist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Teknoluxion</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, AWS SageMaker, S3, Glue, Kafka, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc74ac325008850</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Medallia Strategy Analytics, Analyst</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Medallia</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=279ab2d1e0ede600</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Software Engineer, StorageGRID</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, CI/CD, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b9a7cc93e281359</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Information Security Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>PROBABLYMONSTERS</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a31a6affadc5dff7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer Co-Op</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Campbell's</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf5705f20c99989</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer Co-Op</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Campbell's</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24b448b6b31cd3a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff1ae859febc505</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior AI Scientist</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5ef7572f1319eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior AI Scientist</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddbda58dfd9e21a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12e1559910a13a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-17.xlsx
+++ b/daily_matches/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d62482ae7cddd2</t>
+          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Agents</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>RAG, Redshift, Synapse, Kinesis, CI/CD, Git, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbffc0979d491df9</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Agents</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,89 +566,89 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863d1330bc4e06b9</t>
+          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871f64414211ac77</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7934dbb22311939d</t>
+          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,73 +657,73 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, Docker, Kubernetes, Apache Airflow, CI/CD, Git</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b48675e2894e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cda1d43e4d0c490</t>
+          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Menlo</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25dea91fa4f468b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Data</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cloudforce</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>National Harbor, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Hadoop, Power BI</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,172 +776,172 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582d2762175caa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b47c0d9b5200cba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4967475cc257ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f671a41056161b0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Linux Foundation</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0523d8a73b455a89</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ab07eb4acffa0b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Athena, Redshift, CI/CD, Terraform, Git, Redshift, Kafka, PostgreSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f33a43b908e634</t>
+          <t>https://www.indeed.com/viewjob?jk=5b45b6e8aa67df7c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, AKS, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc9016a88e96d04</t>
+          <t>https://www.indeed.com/viewjob?jk=5d16dbeaec3930ca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Developer, SA</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Snowflake, Kafka, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3bc996c009755</t>
+          <t>https://www.indeed.com/viewjob?jk=90ab5e0fe05ad0e3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML/AI</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bcc722d28f0fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c80d6271afc8362</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Power BI, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96177e962e8cc454</t>
+          <t>https://www.indeed.com/viewjob?jk=45618c98009db818</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44241dafdd1e9110</t>
+          <t>https://www.indeed.com/viewjob?jk=9716207967dcb05a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, NLTK, CI/CD, Python</t>
+          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b112a1e1ee57ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=5a50810716b56812</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (Quality Assurance/SDET Focus)</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957fb31284f4375c</t>
+          <t>https://www.indeed.com/viewjob?jk=463f4a84c24c11ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dc06c5e4d512c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a77f7327e40f07c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - People Strategy &amp; Analytics</t>
+          <t>Senior Software Engineer - Quality</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
+          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0efa2f7bb9ed87</t>
+          <t>https://www.indeed.com/viewjob?jk=4e77d1040263feaf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Scientist, Senior</t>
+          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, MLflow, CI/CD, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48779fae100c0244</t>
+          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI/ML Engineer/ AI Ops Engineer</t>
+          <t>Data Scientist - Investment Team</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Tableau, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854a4d3726897368</t>
+          <t>https://www.indeed.com/viewjob?jk=e45ed06e8629731c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scientist II, Data Science – Behavioral Marketing Analytics &amp; Customer Insights</t>
+          <t>Senior AI/ML Engineer- Hybrid Eden Prairie, MN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+          <t>TensorFlow, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da4d55e5bd9e628</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd2ccc84be9a086</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scientist II, Data Science – Behavioral Marketing Analytics &amp; Customer Insights</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98562f66128c6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a965f517ad9d1869</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Commercial Solution Engineer</t>
+          <t>Java GENAI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50d2aae1ab24a68</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5ac982227c2173</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Sr Architect (Back office)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>xe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,87 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12e1559910a13a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea758999ce39ab4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Analytics Development &amp; Model Governance</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, Git, PySpark, Polars, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=488286dd84e6ed1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d0cc14d2719579a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-17.xlsx
+++ b/daily_matches/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b12b716db62c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9fddafc2634996</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, Kinesis, CI/CD, Git, Snowflake, Databricks, Redshift, PySpark</t>
+          <t>RAG, Copilot, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd4b580c9734c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Full Stack AI Engineer (Data)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, RAG, Pinecone, MLflow, FastAPI, CI/CD, Snowflake, Databricks, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140694c2c64613b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Generative AI, RAG, Docker, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8053306bec847</t>
+          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Senior Architect, Software Engineering — Gateway Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9110ee049f04d732</t>
+          <t>https://www.indeed.com/viewjob?jk=1df263ef60a18bdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>IT Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Tempur + Sealy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Trinity, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6c0d2095fec46b</t>
+          <t>https://www.indeed.com/viewjob?jk=67653c1bffcbc7be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>AI Practitioner- PRN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Rogers Behavioral Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oconomowoc, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423198fafbbced4</t>
+          <t>https://www.indeed.com/viewjob?jk=36826f7fb1097614</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6c34af7f7ba0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b8ac508f0df5cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b47c0d9b5200cba</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e10a703fe725d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f671a41056161b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Engineer II - AI Foundations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ab07eb4acffa0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea762df3fe874ef7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Database Integrations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, BigQuery, Data Lake, Kubernetes, Snowflake, BigQuery, Kafka, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b45b6e8aa67df7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d403b431763eb561</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Docker, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d16dbeaec3930ca</t>
+          <t>https://www.indeed.com/viewjob?jk=00aa466b1ce0cfa2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Sr. ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ab5e0fe05ad0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b2680ad6985da8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c80d6271afc8362</t>
+          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Adv, Enterprise BI Platforms</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45618c98009db818</t>
+          <t>https://www.indeed.com/viewjob?jk=f7085928ac8cd7a7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Software Engineer in Test</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CertiPath Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9716207967dcb05a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1fefe86bdec86b3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Front End Web Developer Senior</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
+          <t>Prompt Engineering, S3, FastAPI, CI/CD, Snowflake, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a50810716b56812</t>
+          <t>https://www.indeed.com/viewjob?jk=fb5d99249f66d2eb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Harbor Compliance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
+          <t>Copilot, Prompt Engineering, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463f4a84c24c11ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1727e08e22717e36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Flowable Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Hike2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Home, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a77f7327e40f07c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf34d30a6f3cc306</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality</t>
+          <t>Quality Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Jenkins, Terraform, Git, Tableau, Power BI, Python, R, Java</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77d1040263feaf</t>
+          <t>https://www.indeed.com/viewjob?jk=9271eae7c71442d0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer Sr (Infrastructure Software Engineer)</t>
+          <t>Senior Data Analyst (part-time)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>LinTech Global, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,252 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dee59f259bc35d</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Scientist - Investment Team</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Millennium Management</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Tableau, Python, SQL, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e45ed06e8629731c</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer- Hybrid Eden Prairie, MN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd2ccc84be9a086</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Terra Quantum</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a965f517ad9d1869</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Java GENAI Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5ac982227c2173</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr Architect (Back office)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>xe</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea758999ce39ab4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Analytics Development &amp; Model Governance</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Experian</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, Git, PySpark, Polars, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=488286dd84e6ed1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Scientist I</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>HDR</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0cc14d2719579a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1921904a6d0a74</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-17.xlsx
+++ b/daily_matches/job_matches_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, S3, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9fddafc2634996</t>
+          <t>https://www.indeed.com/viewjob?jk=9f453eb1bd89d09d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – API &amp; Cloud Integrations (Java, AWS)</t>
+          <t>AI Engineer - Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>WorkCog</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Comfort, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, Kubernetes, AKS, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526bcf8fe154368e</t>
+          <t>https://www.indeed.com/viewjob?jk=f795da03d0dac54f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Data)</t>
+          <t>Engineer Software (Prisma AIRS Backend)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, MLflow, FastAPI, CI/CD, Snowflake, Databricks, Kafka, PostgreSQL</t>
+          <t>BigQuery, Docker, Kubernetes, AKS, CI/CD, Git, BigQuery, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced4fe089b71c6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=17bc6a5de3f2f2f3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Sales Domain (Java / Google Cloud)</t>
+          <t>Junior Developer - Python &amp; Go</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>LangChain, RAG, S3, Glue, Redshift, Docker, CI/CD, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612dbd60844ef3cc</t>
+          <t>https://www.indeed.com/viewjob?jk=173ef8abe0493c5a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering — Gateway Platform</t>
+          <t>Google / CCaaS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Cassandra, NoSQL, SQL</t>
+          <t>RAG, Prompt Engineering, TensorFlow, XGBoost, BigQuery, CI/CD, Terraform, BigQuery, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df263ef60a18bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff55b09035c75812</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Engineer</t>
+          <t>JR. AI ENGINEER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tempur + Sealy</t>
+          <t>REVI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trinity, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, CI/CD, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Pinecone, Prompt Engineering, PyTorch, XGBoost, LightGBM, Kinesis, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67653c1bffcbc7be</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0a61f7d307ef4b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Practitioner- PRN</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rogers Behavioral Health</t>
+          <t>Solifi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oconomowoc, WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36826f7fb1097614</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b5d0142558a5e3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, S3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b8ac508f0df5cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3992218ca4d904a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>AI Engineer – GenAI &amp; Agentic Systems (Officer)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, S3, EC2, Apache Airflow, CI/CD, Databricks, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e10a703fe725d</t>
+          <t>https://www.indeed.com/viewjob?jk=f141152a08943a9a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Forward Deployed Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb9632408d5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=5bae6e6dbebd3dc2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer II - AI Foundations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea762df3fe874ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=b22a15a4ec114479</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Database Integrations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Kubernetes, Snowflake, BigQuery, Kafka, MySQL, MongoDB, SQL</t>
+          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d403b431763eb561</t>
+          <t>https://www.indeed.com/viewjob?jk=090a3307254d29c9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer - Agentic Systems</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aa466b1ce0cfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=50528ca3a22763de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b2680ad6985da8</t>
+          <t>https://www.indeed.com/viewjob?jk=a36b85a7a883f151</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, AI Platform</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3141caec45eab</t>
+          <t>https://www.indeed.com/viewjob?jk=b02d7e468d7513ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Adv, Enterprise BI Platforms</t>
+          <t>SR. AI ENGINEER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>REVI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Kinesis, Docker, Kubernetes, CI/CD, Databricks, Kafka, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7085928ac8cd7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d693521d2d7d7fe9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer in Test</t>
+          <t>Sr Software Engineer, Storage</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CertiPath Inc</t>
+          <t>Cribl</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+          <t>RAG, S3, EC2, Data Lake, CI/CD, Terraform, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1fefe86bdec86b3</t>
+          <t>https://www.indeed.com/viewjob?jk=586c30572073aef6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Front End Web Developer Senior</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prompt Engineering, S3, FastAPI, CI/CD, Snowflake, Python, R, Java, Scala, Optimization</t>
+          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb5d99249f66d2eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3ae634771f2ca2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harbor Compliance</t>
+          <t>Conservation X Labs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1727e08e22717e36</t>
+          <t>https://www.indeed.com/viewjob?jk=33c08a461f2ab07a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Flowable Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hike2</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Home, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf34d30a6f3cc306</t>
+          <t>https://www.indeed.com/viewjob?jk=669552ac14abe463</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Quality Engineer II</t>
+          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, RecSys)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,742 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9271eae7c71442d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6958f5c5a7366355</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (part-time)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LinTech Global, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Peoria, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e64812442158df91</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Peoria, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7a63b818631ba0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Imagine Group, LLC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39b3bfcd8f267eee</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acd6db83a4c4c9f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Agentic AI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, FastAPI, BigQuery, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00964632eba1b2bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Agentic AI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, FastAPI, BigQuery, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bb30d3f397f211e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer- Full Stack Cloud</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMS Holdings</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>York, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c69e3d3607bcfe9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ML Administrator</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Streamline Defense</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Terraform, Git, Databricks, NoSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6229fcbca69a9f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Arlington, VA, US USA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf99a74dcbfafd86</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Analytics Integration Specialist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9f484798a35207</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Grid Data Analyst</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sumter Electric Cooperative, Inc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sumterville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1921904a6d0a74</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Dataflow, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0d8ee680ad7a2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Automation Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3d216a9591fe827</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea51c9c1feafe089</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer III</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=511ad307b7511b25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>eSentire</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=790560588950d4a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Digital S/W Engineer Intm Analyst-Officer (Irving)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, Jenkins, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd49109aea08b050</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Databricks Developer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea896dc6fd17cc57</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arkana Laboratories</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a09d89cac1ca9e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Analytics Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, EC2, CI/CD, PySpark, Polars, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5759e4c33fa3eaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Architect (Hands on)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stratus</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c050b08ab3289d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Circadence Corporation</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tupelo, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df56f750bc722357</t>
         </is>
       </c>
     </row>
